--- a/public/template_pemilih.xlsx
+++ b/public/template_pemilih.xlsx
@@ -15,18 +15,39 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="4">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="11">
   <si>
     <t>NIS</t>
   </si>
   <si>
-    <t>Nama</t>
+    <t>Nama Lengkap</t>
   </si>
   <si>
     <t>Kelas</t>
   </si>
   <si>
     <t>Jenis Kelamin (L/P)</t>
+  </si>
+  <si>
+    <t>Username</t>
+  </si>
+  <si>
+    <t>Password</t>
+  </si>
+  <si>
+    <t>Budi Santoso</t>
+  </si>
+  <si>
+    <t>X IPA 1</t>
+  </si>
+  <si>
+    <t>L</t>
+  </si>
+  <si>
+    <t>budi_santoso</t>
+  </si>
+  <si>
+    <t>budi123</t>
   </si>
 </sst>
 </file>
@@ -50,16 +71,22 @@
       <strike val="0"/>
       <u val="none"/>
       <sz val="11"/>
-      <color rgb="FF000000"/>
+      <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4CAF50"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -76,7 +103,7 @@
   </cellStyleXfs>
   <cellXfs count="2">
     <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="0" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0"/>
-    <xf xfId="0" fontId="1" numFmtId="0" fillId="0" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0"/>
+    <xf xfId="0" fontId="1" numFmtId="0" fillId="2" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -376,10 +403,18 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:D1"/>
+  <dimension ref="A1:F2"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col min="1" max="1" width="15" customWidth="true" style="0"/>
+    <col min="2" max="2" width="30" customWidth="true" style="0"/>
+    <col min="3" max="3" width="15" customWidth="true" style="0"/>
+    <col min="4" max="4" width="20" customWidth="true" style="0"/>
+    <col min="5" max="5" width="20" customWidth="true" style="0"/>
+    <col min="6" max="6" width="20" customWidth="true" style="0"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" spans="1:6">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -391,6 +426,32 @@
       </c>
       <c r="D1" s="1" t="s">
         <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6">
+      <c r="A2">
+        <v>1001</v>
+      </c>
+      <c r="B2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F2" t="s">
+        <v>10</v>
       </c>
     </row>
   </sheetData>

--- a/public/template_pemilih.xlsx
+++ b/public/template_pemilih.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="13">
   <si>
     <t>NIS</t>
   </si>
@@ -35,6 +35,9 @@
     <t>Password</t>
   </si>
   <si>
+    <t>Kode Akses</t>
+  </si>
+  <si>
     <t>Budi Santoso</t>
   </si>
   <si>
@@ -48,6 +51,9 @@
   </si>
   <si>
     <t>budi123</t>
+  </si>
+  <si>
+    <t>BUDI12</t>
   </si>
 </sst>
 </file>
@@ -403,7 +409,7 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:G2"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="15" customWidth="true" style="0"/>
@@ -412,9 +418,10 @@
     <col min="4" max="4" width="20" customWidth="true" style="0"/>
     <col min="5" max="5" width="20" customWidth="true" style="0"/>
     <col min="6" max="6" width="20" customWidth="true" style="0"/>
+    <col min="7" max="7" width="20" customWidth="true" style="0"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:7">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -433,25 +440,31 @@
       <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
     </row>
-    <row r="2" spans="1:6">
+    <row r="2" spans="1:7">
       <c r="A2">
         <v>1001</v>
       </c>
       <c r="B2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F2" t="s">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="G2" t="s">
+        <v>12</v>
       </c>
     </row>
   </sheetData>
